--- a/Quan Trac Lun/Data/HD XL01/KM0+100.xlsx
+++ b/Quan Trac Lun/Data/HD XL01/KM0+100.xlsx
@@ -1,43 +1,232 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Data\HD XL01\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38ED9806-448D-420D-BF6B-50556477A24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
+  <si>
+    <t>BIỂU GHI ĐO QUAN TRẮC LÚN</t>
+  </si>
+  <si>
+    <t>Người lập:</t>
+  </si>
+  <si>
+    <t>Tên mốc:</t>
+  </si>
+  <si>
+    <t>Thời tiết:</t>
+  </si>
+  <si>
+    <t>Cao độ mốc:</t>
+  </si>
+  <si>
+    <t>Lý trình:</t>
+  </si>
+  <si>
+    <t>Km34+120</t>
+  </si>
+  <si>
+    <t>Ngày đặt bàn:</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>Cao độ mốc</t>
+  </si>
+  <si>
+    <t>Số đọc mia tại mốc</t>
+  </si>
+  <si>
+    <t>Cao độ đường ngắm</t>
+  </si>
+  <si>
+    <t>Số đọc mia quan trắc</t>
+  </si>
+  <si>
+    <t>Cao độ đỉnh cần</t>
+  </si>
+  <si>
+    <t>Chiều dài cần</t>
+  </si>
+  <si>
+    <t>Cao độ bàn đo lún</t>
+  </si>
+  <si>
+    <t>Độ lún hàng ngày</t>
+  </si>
+  <si>
+    <t>Tổng độ lún</t>
+  </si>
+  <si>
+    <t>Cao độ nền đường</t>
+  </si>
+  <si>
+    <t>Chiều dày lớp đắp</t>
+  </si>
+  <si>
+    <t>Chiều dày đắp</t>
+  </si>
+  <si>
+    <t>Xác nhận kiểm tra</t>
+  </si>
+  <si>
+    <t>Trái</t>
+  </si>
+  <si>
+    <t>Tim</t>
+  </si>
+  <si>
+    <t>Phải</t>
+  </si>
+  <si>
+    <t>Nhà thầu</t>
+  </si>
+  <si>
+    <t>TVGS</t>
+  </si>
+  <si>
+    <t>(m)</t>
+  </si>
+  <si>
+    <t>( mm)</t>
+  </si>
+  <si>
+    <t>Ngày Quan trắc</t>
+  </si>
+  <si>
+    <t>DỰ ÁN THÀNH PHẦN ĐOẠN HẬU GIANG - CÀ MAU
+THUỘC DỰ ÁN XÂY DỰNG CÔNG TRÌNH ĐƯỜNG BỘ CAO TỐC BẮC - NAM PHÍA ĐÔNG GIAI ĐOẠN 2021 - 2025</t>
+  </si>
+  <si>
+    <t>GÓI THẦU XL03 :THI CÔNG XÂY DỰNG ĐOẠN TUYẾN KM114+200 - KM126+223 BAO GỒM TUYẾN NỐI NÚT GIAO IC12  VỚI QL1 (BAO GỒM KHẢO SÁT, THIẾT KẾ BVTC)</t>
+  </si>
+  <si>
+    <t>NHÀ THẦU: LIÊN DANH PHÂN VIỆN KHCN GTVT PHÍA NAM - CÔNG TY CỔ PHẦN TƯ VẤN KỸ THUẬT VÀ XÂY DỰNG HỒNG HÀ</t>
+  </si>
+  <si>
+    <t>KM0+100</t>
+  </si>
+  <si>
+    <t>05/07/2025</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -45,15 +234,403 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规_Sheet1" xfId="2" xr:uid="{F564A963-D938-4BDB-8422-2926EDB2141E}"/>
+    <cellStyle name="常规_路堤稳定和沉降观测 - 沉降板" xfId="1" xr:uid="{C4C317B3-BEDA-49EC-99ED-7CD8322E30CE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -79,39 +656,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -144,9 +721,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -179,6 +773,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -240,13 +851,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -255,6 +859,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -319,21 +930,598 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B528856B-9B6A-48DF-ACF2-DE4C5267C4D4}">
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AB11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="18" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
+      <c r="A1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="28"/>
+    </row>
+    <row r="2" spans="1:28" ht="17.25">
+      <c r="A2" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="31"/>
+    </row>
+    <row r="3" spans="1:28" ht="17.25">
+      <c r="A3" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="31"/>
+    </row>
+    <row r="4" spans="1:28" ht="17.25">
+      <c r="A4" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="34"/>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="4"/>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="T6" s="8">
+        <v>835</v>
+      </c>
+      <c r="U6" s="7"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="9"/>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="10"/>
+      <c r="T7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="13"/>
+    </row>
+    <row r="8" spans="1:28" ht="13.9" customHeight="1">
+      <c r="A8" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="21"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="S8" s="24"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="V8" s="24"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA8" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB8" s="25"/>
+    </row>
+    <row r="9" spans="1:28" ht="30">
+      <c r="A9" s="42"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB9" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="43"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="U10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="V10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="W10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="X10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="17"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1">
+        <v>835</v>
+      </c>
+      <c r="D11" s="1">
+        <v>500</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>3</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1">
+        <v>4</v>
+      </c>
+      <c r="P11" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>4</v>
+      </c>
+      <c r="R11" s="1">
+        <v>5</v>
+      </c>
+      <c r="S11" s="1">
+        <v>5</v>
+      </c>
+      <c r="T11" s="1">
+        <v>5</v>
+      </c>
+      <c r="U11" s="1">
+        <v>6</v>
+      </c>
+      <c r="V11" s="1">
+        <v>6</v>
+      </c>
+      <c r="W11" s="1">
+        <v>6</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="A3:AB3"/>
+    <mergeCell ref="A4:AB4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+  </mergeCells>
+  <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Quan Trac Lun/Data/HD XL01/KM0+100.xlsx
+++ b/Quan Trac Lun/Data/HD XL01/KM0+100.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vba\bketech\Quan Trac Lun\Data\HD XL01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBA Project\bketech\Quan Trac Lun\Data\HD XL01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38ED9806-448D-420D-BF6B-50556477A24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FF0D43-B88F-4BD2-9AF3-D095CC169C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8325" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C402617-1403-418F-9928-C6EF4DD57BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -170,14 +170,14 @@
       <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -186,7 +186,7 @@
       <u/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -194,20 +194,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -554,15 +554,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -624,6 +615,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -966,147 +966,147 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="18" customWidth="1"/>
-    <col min="3" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.69921875" style="18" customWidth="1"/>
+    <col min="3" max="16384" width="8.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.450000000000003" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:28" ht="32.4" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="28"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="25"/>
     </row>
-    <row r="2" spans="1:28" ht="17.25">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:28" ht="16.8">
+      <c r="A2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="31"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="28"/>
     </row>
-    <row r="3" spans="1:28" ht="17.25">
-      <c r="A3" s="29" t="s">
+    <row r="3" spans="1:28" ht="16.8">
+      <c r="A3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="31"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="28"/>
     </row>
-    <row r="4" spans="1:28" ht="17.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:28" ht="16.8">
+      <c r="A4" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="34"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="31"/>
     </row>
     <row r="5" spans="1:28">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1136,11 +1136,11 @@
       <c r="AB5" s="4"/>
     </row>
     <row r="6" spans="1:28">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -1172,13 +1172,13 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:28">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="10" t="s">
         <v>33</v>
       </c>
@@ -1211,17 +1211,17 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="13"/>
     </row>
-    <row r="8" spans="1:28" ht="13.9" customHeight="1">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:28" ht="13.95" customHeight="1">
+      <c r="A8" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="38" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="19" t="s">
@@ -1247,16 +1247,16 @@
       </c>
       <c r="P8" s="21"/>
       <c r="Q8" s="22"/>
-      <c r="R8" s="23" t="s">
+      <c r="R8" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="23" t="s">
+      <c r="S8" s="46"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="V8" s="24"/>
-      <c r="W8" s="25"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="45"/>
       <c r="X8" s="19" t="s">
         <v>18</v>
       </c>
@@ -1266,16 +1266,16 @@
       <c r="Z8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="23" t="s">
+      <c r="AA8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="25"/>
+      <c r="AB8" s="45"/>
     </row>
-    <row r="9" spans="1:28" ht="30">
-      <c r="A9" s="42"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+    <row r="9" spans="1:28">
+      <c r="A9" s="39"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
       <c r="E9" s="19"/>
       <c r="F9" s="14" t="s">
         <v>22</v>
@@ -1342,8 +1342,8 @@
       </c>
     </row>
     <row r="10" spans="1:28">
-      <c r="A10" s="43"/>
-      <c r="B10" s="46"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="43"/>
       <c r="C10" s="16" t="s">
         <v>27</v>
       </c>
@@ -1498,6 +1498,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
@@ -1514,12 +1520,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="7.874015748031496E-2" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
